--- a/01_analyses_states/Chhattisgarh/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Chhattisgarh/results/SoIB_summaries.xlsx
@@ -558,10 +558,10 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -569,10 +569,10 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="C8">
-        <v>354</v>
+        <v>363</v>
       </c>
     </row>
   </sheetData>
@@ -667,7 +667,7 @@
         <v>23</v>
       </c>
       <c r="B2">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -675,7 +675,7 @@
         <v>18</v>
       </c>
       <c r="B3">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -683,7 +683,7 @@
         <v>24</v>
       </c>
       <c r="B4">
-        <v>433</v>
+        <v>439</v>
       </c>
     </row>
   </sheetData>
@@ -712,7 +712,7 @@
         <v>28</v>
       </c>
       <c r="B2">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -720,7 +720,7 @@
         <v>29</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -731,7 +731,7 @@
         <v>30</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -777,16 +777,16 @@
         <v>37</v>
       </c>
       <c r="B2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C2">
-        <v>77.40000000000001</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="D2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E2">
-        <v>81.2</v>
+        <v>81.40000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -797,13 +797,13 @@
         <v>24</v>
       </c>
       <c r="C3">
-        <v>22.6</v>
+        <v>22.4</v>
       </c>
       <c r="D3">
         <v>19</v>
       </c>
       <c r="E3">
-        <v>18.8</v>
+        <v>18.6</v>
       </c>
     </row>
   </sheetData>
